--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02DF6B7-2C94-4877-A657-D226A42FD454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194D4221-49D4-4F60-9272-8006441E601F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4992" yWindow="2988" windowWidth="23040" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="3660" windowWidth="23040" windowHeight="12660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hero" sheetId="1" r:id="rId1"/>
+    <sheet name="HeroAttribute" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,13 +115,33 @@
   <si>
     <t>BaseAttack</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui://Hero/Hero_1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui://Hero/Hero_1002</t>
+  </si>
+  <si>
+    <t>ui://Hero/Hero_1003</t>
+  </si>
+  <si>
+    <t>ui://Hero/Hero_1004</t>
+  </si>
+  <si>
+    <t>ui://Hero/Hero_1005</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +168,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -179,10 +207,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -463,98 +495,276 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:K10"/>
+  <sheetFormatPr defaultColWidth="15.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="23.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>1001</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>1002</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>1003</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>1004</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>1005</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B0E0CF-ACF9-4F8A-806F-ED1C3C9B80FF}">
   <dimension ref="C3:I10"/>
-  <sheetFormatPr defaultColWidth="15.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>1001</v>
       </c>
       <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6">
+      <c r="E6">
         <v>500</v>
       </c>
-      <c r="I6">
+      <c r="F6">
         <v>20</v>
       </c>
     </row>
@@ -563,21 +773,12 @@
         <v>1002</v>
       </c>
       <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
         <v>4.3</v>
       </c>
-      <c r="H7">
+      <c r="E7">
         <v>1000</v>
       </c>
-      <c r="I7">
+      <c r="F7">
         <v>10</v>
       </c>
     </row>
@@ -586,21 +787,12 @@
         <v>1003</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
         <v>4.3</v>
       </c>
-      <c r="H8">
+      <c r="E8">
         <v>500</v>
       </c>
-      <c r="I8">
+      <c r="F8">
         <v>15</v>
       </c>
     </row>
@@ -609,21 +801,12 @@
         <v>1004</v>
       </c>
       <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
         <v>3.5</v>
       </c>
-      <c r="H9">
+      <c r="E9">
         <v>400</v>
       </c>
-      <c r="I9">
+      <c r="F9">
         <v>20</v>
       </c>
     </row>
@@ -632,21 +815,12 @@
         <v>1005</v>
       </c>
       <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10">
+      <c r="E10">
         <v>500</v>
       </c>
-      <c r="I10">
+      <c r="F10">
         <v>20</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194D4221-49D4-4F60-9272-8006441E601F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F423C6-9A2B-46E1-902A-5E603DEF5511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="3660" windowWidth="23040" windowHeight="12660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2568" yWindow="3528" windowWidth="23040" windowHeight="12660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hero" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,34 +89,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>基础速度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseSpeed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseHP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础攻击力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseAttack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -135,6 +107,38 @@
   </si>
   <si>
     <t>ui://Hero/Hero_1005</t>
+  </si>
+  <si>
+    <t>AttributeDict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dictionary&lt;int, long&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#实际属性值需要除去10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000:50000,1002:5000000,1011:45000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000:43000,1002:8000000,1011:37000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000:47000,1002:6000000,1011:40000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000:40000,1002:4500000,1011:50000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000:55000,1002:5000000,1011:45000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -211,10 +215,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -495,26 +499,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:K10"/>
+  <dimension ref="C3:J10"/>
   <sheetFormatPr defaultColWidth="15.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="23.5546875" customWidth="1"/>
     <col min="10" max="10" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,14 +520,13 @@
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -549,14 +540,13 @@
         <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
@@ -575,9 +565,8 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>1001</v>
       </c>
@@ -590,15 +579,12 @@
       <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>1002</v>
       </c>
@@ -611,15 +597,12 @@
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>1003</v>
       </c>
@@ -632,15 +615,12 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="G8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>1004</v>
       </c>
@@ -653,15 +633,12 @@
       <c r="F9" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>1005</v>
       </c>
@@ -674,13 +651,10 @@
       <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="5"/>
+      <c r="G10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -691,11 +665,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B0E0CF-ACF9-4F8A-806F-ED1C3C9B80FF}">
-  <dimension ref="C3:I10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="55" style="5" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
@@ -703,125 +677,88 @@
     <col min="9" max="9" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C3" s="6" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C4" s="6" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C5" s="6" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="D5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>1001</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>500</v>
-      </c>
-      <c r="F6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>1002</v>
       </c>
-      <c r="D7">
-        <v>4.3</v>
-      </c>
-      <c r="E7">
-        <v>1000</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D7" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>1003</v>
       </c>
-      <c r="D8">
-        <v>4.3</v>
-      </c>
-      <c r="E8">
-        <v>500</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>1004</v>
       </c>
-      <c r="D9">
-        <v>3.5</v>
-      </c>
-      <c r="E9">
-        <v>400</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>1005</v>
       </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10">
-        <v>500</v>
-      </c>
-      <c r="F10">
-        <v>20</v>
+      <c r="D10" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
